--- a/artfynd/A 48292-2023 artfynd.xlsx
+++ b/artfynd/A 48292-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48292-2023 artfynd.xlsx
+++ b/artfynd/A 48292-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102049125</v>
+        <v>102049114</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>414100.681458688</v>
+        <v>414091</v>
       </c>
       <c r="R2" t="n">
-        <v>6690683.52956525</v>
+        <v>6690685</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102049114</v>
+        <v>102049116</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>414090.8012715838</v>
+        <v>414136</v>
       </c>
       <c r="R3" t="n">
-        <v>6690685.248515969</v>
+        <v>6690703</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102049116</v>
+        <v>102049123</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>414135.3679920626</v>
+        <v>414113</v>
       </c>
       <c r="R4" t="n">
-        <v>6690703.01480318</v>
+        <v>6690703</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102049123</v>
+        <v>102049125</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>414112.5396770494</v>
+        <v>414101</v>
       </c>
       <c r="R5" t="n">
-        <v>6690702.563202592</v>
+        <v>6690683</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 48292-2023 artfynd.xlsx
+++ b/artfynd/A 48292-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102049114</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102049116</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102049123</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102049125</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>